--- a/data.xlsx
+++ b/data.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="120">
   <si>
     <t>ITEM</t>
   </si>
@@ -255,67 +255,169 @@
 3.视频输入/输出最大分辨率：HDCP 1920*1080@60Hz；HDTV 1920*1080@60Hz</t>
   </si>
   <si>
-    <t>6路高清视频综合单元</t>
-  </si>
-  <si>
-    <t>DC-A06-E</t>
+    <t>6路高清视频解码器H系列</t>
+  </si>
+  <si>
+    <t>DC-A06-H</t>
   </si>
   <si>
     <t>6路高清视频解码器</t>
   </si>
   <si>
-    <t>1.采用嵌入式Linux 操作系统，支持7×24 小时稳定运行
-2.视频输入输出接口：HDMI IN*4、HDMI OUT*6
-3.解码能力：支持H.265、H.264、MPEG4格式解码，整机最高支持8路1200W@20HZ/8路4K@30HZ/32路1080P@30HZ/72路720P@30HZ同时解码
-4.HDMI输入分辨率：最高可达3840x2160@30HZ、1920X1080@60HZ
-5.DVI输入分辨率：最高可达1920X1080@60HZ、1920X1080@50HZ
-6.HDMI输出分辨率：最高可达3840x2160@30HZ（第3/6/9/12口不支持4K@30HZ）、1920X1200@60HZ
-7.网络协议：支持TCP/IP、RTSP、UDP、HTTP、Telnet、ICMP、ARP、SIP、SNMP、FTP、TFTP、ONVIF、NTP协议接入
-8.支持开窗、漫游、画中画、分屏、拼接上墙及虚拟LED，支持小间距LED显示、大屏开关机功能
-9.支持G.711A、G.711U 音频格式解码输出
-10.支持2个10M/100M/1000M Base-T自适应的RJ45以太网口</t>
-  </si>
-  <si>
-    <t>9路高清视频综合单元</t>
-  </si>
-  <si>
-    <t>DC-A09-E</t>
+    <t xml:space="preserve">输入路数:2路HDMI
+视频输入分辨率:所有接口支持：3840*2160（4K）@60Hz、3840*2160（4K）@30Hz、1920*1200（WUXGA）@60Hz、1920*1080（1080P）@60Hz、1920*1080（1080P）@50Hz、1920*1080（1080P）@30Hz、1600*1200（UXGA）@60Hz、1440*900（WXGA+）@60Hz、1280*1024（SXGA）@60Hz、1280*720（720P）@60Hz、1280*720（720P）@50Hz、1024*768（XGA）@60Hz
+输出路数:6路HDMI
+视频输出分辨率:所有接口支持：3840*2160（4K）@60Hz、3840*2160（4K）@30Hz、1920*1200（WUXGA）@60Hz、1920*1080（1080P）@60Hz、1600*1200（UXGA）@60Hz、1440*900（WXGA+）@60Hz、1280*1024（SXGA）@60Hz、1280*720（720P）@60Hz、1024*768（XGA）@60Hz
+解码格式:H.265、H.264、MPEG4
+解码能力:2*8K@30Hz/12*1200W@20Hz/12*4K@30Hz/24*400W@30Hz/31*300W@30Hz/48*1080P@30Hz/96*720P@30Hz/216*D1@30Hz
+拼接功能:M*N（总数不超过最大输出口个数）
+多组电视墙:单机可建立管理4个配置不同的电视墙
+场景管理:可保存64个场景
+音频输入:1路凤凰端子音频输入（预留）
+1路3.5mm音频输入
+告警输入:4路凤凰端子告警输入（预留）
+音频输出:1路凤凰端子音频输出（预留）
+1路3.5mm音频输出，左右双声道
+告警输出:4路凤凰端子告警输出（预留）
+串口:2个（1个RJ45 RS232，另一个RJ45 RS232 Console和RS485合用）
+网络接口:2个GE网口，RJ45接口，半双工/全双工以太网，支持10M/100M/1000M Base-T自适应
+USB接口:2个USB3.0接口
+产品尺寸（W*H*D）（mm）:440*48*343.9
+重量（Kg）:3.773
+整机功耗（W）:30.89
+</t>
+  </si>
+  <si>
+    <t>9路高清视频解码器H系列</t>
+  </si>
+  <si>
+    <t>DC-A09-H</t>
   </si>
   <si>
     <t>9路高清视频解码器</t>
   </si>
   <si>
-    <t>1.采用嵌入式Linux 操作系统，支持7×24 小时稳定运行
-2.视频输入输出接口：HDMI IN*4、HDMI OUT*9
-3.解码能力：支持H.265、H.264、MPEG4格式解码，整机最高支持12路1200W@20HZ/12路4K@30HZ/48路1080P@30HZ/108路720P@30HZ同时解码
-4.HDMI输入分辨率：最高可达3840x2160@30HZ、1920X1080@60HZ
-5.DVI输入分辨率：最高可达1920X1080@60HZ、1920X1080@50HZ
-6.HDMI输出分辨率：最高可达3840x2160@30HZ（第3/6/9/12口不支持4K@30HZ）、1920X1200@60HZ
-7.网络协议：支持TCP/IP、RTSP、UDP、HTTP、Telnet、ICMP、ARP、SIP、SNMP、FTP、TFTP、ONVIF、NTP协议接入
-8.支持开窗、漫游、画中画、分屏、拼接上墙及虚拟LED，支持小间距LED显示、大屏开关机功能
-9.支持G.711A、G.711U 音频格式解码输出
-10.支持2个10M/100M/1000M Base-T自适应的RJ45以太网口</t>
-  </si>
-  <si>
-    <t>12路高清视频综合单元</t>
-  </si>
-  <si>
-    <t>DC-A12-E</t>
+    <t xml:space="preserve">输入路数:3路HDMI
+视频输入分辨率:所有接口支持：3840*2160（4K）@60Hz、3840*2160（4K）@30Hz、1920*1200（WUXGA）@60Hz、1920*1080（1080P）@60Hz、1920*1080（1080P）@50Hz、1920*1080（1080P）@30Hz、1600*1200（UXGA）@60Hz、1440*900（WXGA+）@60Hz、1280*1024（SXGA）@60Hz、1280*720（720P）@60Hz、1280*720（720P）@50Hz、1024*768（XGA）@60Hz
+输出路数:9路HDMI
+视频输出分辨率:所有接口支持：3840*2160（4K）@60Hz、3840*2160（4K）@30Hz、1920*1200（WUXGA）@60Hz、1920*1080（1080P）@60Hz、1600*1200（UXGA）@60Hz、1440*900（WXGA+）@60Hz、1280*1024（SXGA）@60Hz、1280*720（720P）@60Hz、1024*768（XGA）@60Hz
+解码格式:H.265、H.264、MPEG4
+解码能力:3*8K@30Hz/18*1200W@20Hz/18*4K@30Hz/36*400W@30HZ/47*300W@30HZ/72*1080P@30Hz/144*720P@30Hz/324*D1@30Hz
+拼接功能:M*N（总数不超过最大输出口个数）
+多组电视墙:单机可建立管理4个配置不同的电视墙
+场景管理:可保存64个场景
+音频输入:1路凤凰端子音频输入（预留）
+1路3.5mm音频输入
+告警输入:4路凤凰端子告警输入（预留）
+音频输出:1路凤凰端子音频输出（预留）
+1路3.5mm音频输出，左右双声道
+告警输出:4路凤凰端子告警输出（预留）
+串口:2个（1个RJ45 RS232，另一个RJ45 RS232 Console和RS485合用）
+网络接口:2个GE网口，RJ45接口，半双工/全双工以太网，支持10M/100M/1000M Base-T自适应
+USB接口:2个USB3.0接口
+产品尺寸（W*H*D）（mm）:440*48*343.9
+重量（Kg）:3.773
+整机功耗（W）:34.76
+</t>
+  </si>
+  <si>
+    <t>12路高清视频解码器H系列</t>
+  </si>
+  <si>
+    <t>DC-A12-H</t>
   </si>
   <si>
     <t>12路高清视频解码器</t>
   </si>
   <si>
-    <t>1.采用嵌入式Linux 操作系统，支持7×24 小时稳定运行
-2.视频输入输出接口：HDMI IN*4、HDMI OUT*12
-3.解码能力：支持H.265、H.264、MPEG4格式解码，整机最高支持16路1200W@20HZ/16路4K@30HZ/64路1080P@30HZ/144路720P@30HZ同时解码
-4.HDMI输入分辨率：最高可达3840x2160@30HZ、1920X1080@60HZ
-5.DVI输入分辨率：最高可达1920X1080@60HZ、1920X1080@50HZ
-6.HDMI输出分辨率：最高可达3840x2160@30HZ（第3/6/9/12口不支持4K@30HZ）、1920X1200@60HZ
-7.网络协议：支持TCP/IP、RTSP、UDP、HTTP、Telnet、ICMP、ARP、SIP、SNMP、FTP、TFTP、ONVIF、NTP协议接入
-8.支持开窗、漫游、画中画、分屏、拼接上墙及虚拟LED，支持小间距LED显示、大屏开关机功能
-9.支持G.711A、G.711U 音频格式解码输出
-10.支持2个10M/100M/1000M Base-T自适应的RJ45以太网口</t>
+    <t xml:space="preserve">输入路数:4路HDMI
+视频输入分辨率:所有接口支持：3840*2160（4K）@60Hz、3840*2160（4K）@30Hz、1920*1200（WUXGA）@60Hz、1920*1080（1080P）@60Hz、1920*1080（1080P）@50Hz、1920*1080（1080P）@30Hz、1600*1200（UXGA）@60Hz、1440*900（WXGA+）@60Hz、1280*1024（SXGA）@60Hz、1280*720（720P）@60Hz、1280*720（720P）@50Hz、1024*768（XGA）@60Hz
+输出路数:12路HDMI
+视频输出分辨率:所有接口支持：3840*2160（4K）@60Hz、3840*2160（4K）@30Hz、1920*1200（WUXGA）@60Hz、1920*1080（1080P）@60Hz、1600*1200（UXGA）@60Hz、1440*900（WXGA+）@60Hz、1280*1024（SXGA）@60Hz、1280*720（720P）@60Hz、1024*768（XGA）@60Hz
+解码格式:H.265、H.264、MPEG4
+解码能力:4*8K@30Hz/24*1200W@20Hz/24*4K@30Hz/48*400W@30Hz/63*300W@30Hz/96*1080P@30Hz/192*720P@30Hz/432*D1@30Hz
+拼接功能:M*N（总数不超过最大输出口个数）
+多组电视墙:单机可建立管理4个配置不同的电视墙
+场景管理:可保存64个场景
+音频输入:1路凤凰端子音频输入（预留）
+1路3.5mm音频输入
+告警输入:4路凤凰端子告警输入（预留）
+音频输出:1路凤凰端子音频输出（预留）
+1路3.5mm音频输出，左右双声道
+告警输出:4路凤凰端子告警输出（预留）
+串口:2个（1个RJ45 RS232，另一个RJ45 RS232 Console和RS485合用）
+网络接口:2个GE网口，RJ45接口，半双工/全双工以太网，支持10M/100M/1000M Base-T自适应
+USB接口:2个USB3.0接口
+产品尺寸（W*H*D）（mm）:440*48*343.9
+重量（Kg）:3.773
+整机功耗（W）:46.63
+</t>
+  </si>
+  <si>
+    <t>15路高清视频解码器H系列</t>
+  </si>
+  <si>
+    <t>DC-A15-H</t>
+  </si>
+  <si>
+    <t>15路高清视频解码器</t>
+  </si>
+  <si>
+    <t xml:space="preserve">输入路数:5路HDMI
+视频输入分辨率:所有接口支持：3840*2160（4K）@60Hz、3840*2160（4K）@30Hz、1920*1200（WUXGA）@60Hz、1920*1080（1080P）@60Hz、1920*1080（1080P）@50Hz、1920*1080（1080P）@30Hz、1600*1200（UXGA）@60Hz、1440*900（WXGA+）@60Hz、1280*1024（SXGA）@60Hz、1280*720（720P）@60Hz、1280*720（720P）@50Hz、1024*768（XGA）@60Hz
+输出路数:15路HDMI
+视频输出分辨率:所有接口支持：3840*2160（4K）@60Hz、3840*2160（4K）@30Hz、1920*1200（WUXGA）@60Hz、1920*1080（1080P）@60Hz、1600*1200（UXGA）@60Hz、1440*900（WXGA+）@60Hz、1280*1024（SXGA）@60Hz、1280*720（720P）@60Hz、1024*768（XGA）@60Hz
+解码格式:H.265、H.264、MPEG4
+解码能力:5*8K@30Hz/30*1200W@20Hz/30*4K@30Hz/60*400W@30HZ/78*300W@30HZ/120*1080P@30Hz/240*720P@30Hz/540*D1@30Hz
+拼接功能:M*N（总数不超过最大输出口个数）
+多组电视墙:单机可建立管理4个配置不同的电视墙
+场景管理:可保存64个场景
+音频输入:1路凤凰端子音频输入（预留）
+1路3.5mm音频输入
+告警输入:4路凤凰端子告警输入（预留）
+音频输出:1路凤凰端子音频输出（预留）
+1路3.5mm音频输出，左右双声道
+告警输出:4路凤凰端子告警输出（预留）
+串口:2个（1个RJ45 RS232，另一个RJ45 RS232 Console和RS485合用）
+网络接口:2个GE网口，RJ45接口，半双工/全双工以太网，支持10M/100M/1000M Base-T自适应
+USB接口:2个USB3.0接口
+产品尺寸（W*H*D）（mm）:442*88.3*355.7
+重量（Kg）:4.946
+整机功耗（W）:73.34
+</t>
+  </si>
+  <si>
+    <t>18路高清视频解码器H系列</t>
+  </si>
+  <si>
+    <t>DC-A18-H</t>
+  </si>
+  <si>
+    <t>18路高清视频解码器</t>
+  </si>
+  <si>
+    <t xml:space="preserve">输入路数:6路HDMI
+视频输入分辨率:所有接口支持：3840*2160（4K）@60Hz、3840*2160（4K）@30Hz、1920*1200（WUXGA）@60Hz、1920*1080（1080P）@60Hz、1920*1080（1080P）@50Hz、1920*1080（1080P）@30Hz、1600*1200（UXGA）@60Hz、1440*900（WXGA+）@60Hz、1280*1024（SXGA）@60Hz、1280*720（720P）@60Hz、1280*720（720P）@50Hz、1024*768（XGA）@60Hz
+输出路数:18路HDMI
+视频输出分辨率:所有接口支持：3840*2160（4K）@60Hz、3840*2160（4K）@30Hz、1920*1200（WUXGA）@60Hz、1920*1080（1080P）@60Hz、1600*1200（UXGA）@60Hz、1440*900（WXGA+）@60Hz、1280*1024（SXGA）@60Hz、1280*720（720P）@60Hz、1024*768（XGA）@60Hz
+解码格式:H.265、H.264、MPEG4
+解码能力:6*8K@30Hz/36*1200W@20Hz/36*4K@30Hz/72*400W@30HZ/94*300W@30HZ/144*1080P@30Hz/288*720P@30Hz/648*D1@30Hz
+拼接功能:M*N（总数不超过最大输出口个数）
+多组电视墙:单机可建立管理4个配置不同的电视墙
+场景管理:可保存64个场景
+音频输入:1路凤凰端子音频输入（预留）
+1路3.5mm音频输入
+告警输入:4路凤凰端子告警输入（预留）
+音频输出:1路凤凰端子音频输出（预留）
+1路3.5mm音频输出，左右双声道
+告警输出:4路凤凰端子告警输出（预留）
+串口:2个（1个RJ45 RS232，另一个RJ45 RS232 Console和RS485合用）
+网络接口:2个GE网口，RJ45接口，半双工/全双工以太网，支持10M/100M/1000M Base-T自适应
+USB接口:2个USB3.0接口
+产品尺寸（W*H*D）（mm）:442*88.3*355.7
+重量（Kg）:4.946
+整机功耗（W）:82.21
+</t>
   </si>
   <si>
     <t>4路高清视频解码器</t>
@@ -369,13 +471,68 @@
     <t>DAPING</t>
   </si>
   <si>
-    <t>55寸3.5拼缝液晶拼接屏（S1G@F）</t>
+    <t>55寸3.5mm拼缝液晶拼接屏（LS1）</t>
+  </si>
+  <si>
+    <t>MW-D55-LS1</t>
+  </si>
+  <si>
+    <t>55寸3.5拼缝液晶拼接屏</t>
+  </si>
+  <si>
+    <t>1.面板尺寸（inches）:55
+2.拼缝（mm）:3.5
+3.分辨率:1920*1080
+4.色彩数:16.7M
+5.亮度（cd/m²）:300
+6.对比度:1200：1
+7.响应时间（ms）:8
+8.刷新率:60Hz
+9.视角（H/V）:178°/178°
+10.视频输入:HDMI*1（最高分辨率：1920*1080@60Hz），RJ45*1（预留）
+11.其它接口:USB 2.0*1，RS232*3（RJ45接头）
+12.显示点距（mm）:0.63（H）*0.63（V）
+13.供电要求:AC200-240V 50/60Hz
+14.整机功耗（W）:101.8
+15.产品尺寸（W*H*D）（mm）:1213.5*684.3*89.89
+16.重量（Kg）:单台净重：14.6
+17.工作温度:0~40摄氏度
+18.工作湿度:20%--90%(无凝露)
+19.储存温度:-20℃～60℃
+20.储存湿度:10%--90%(无凝露)
+21.使用寿命（h）:30000</t>
+  </si>
+  <si>
+    <t>46寸3.5mm拼缝液晶拼接屏（LS1）</t>
+  </si>
+  <si>
+    <t>MW-D46-LS1</t>
+  </si>
+  <si>
+    <t>46寸3.5拼缝液晶拼接屏</t>
+  </si>
+  <si>
+    <t>1.面板尺寸（inches）:46
+2.拼缝（mm）:3.5
+3.分辨率:1920*1080
+4.色彩数:16.7M
+5.亮度（cd/m²）:300
+6.对比度:1200：1
+7.响应时间（ms）:8
+8.刷新率:60Hz
+9.视角（H/V）:178°/178°
+10.视频输入:HDMI*1（最高分辨率：1920*1080@60Hz），RJ45*1（预留）
+11.其它接口:USB 2.0*1，RS232*3（RJ45接头）
+12.显示点距（mm）:0.53（H）*0.53（V）
+13.供电要求:AC200-240V 50/60Hz
+14.整机功耗（W）:93
+15.产品尺寸（W*H*D）（mm）:1022.18*576.77*84.27</t>
+  </si>
+  <si>
+    <t>55寸3.5mm拼缝液晶拼接屏（S1G@F）</t>
   </si>
   <si>
     <t>MW-D55-S1G</t>
-  </si>
-  <si>
-    <t>55寸3.5拼缝液晶拼接屏</t>
   </si>
   <si>
     <t>1. 面板尺寸(英寸):55
@@ -391,13 +548,10 @@
 11. 重量(kg):14.6</t>
   </si>
   <si>
-    <t>46寸3.5拼缝液晶拼接屏（S1G@F）</t>
+    <t>46寸3.5mm拼缝液晶拼接屏（S1G@F）</t>
   </si>
   <si>
     <t>MW-D46-S1G</t>
-  </si>
-  <si>
-    <t>46寸3.5拼缝液晶拼接屏</t>
   </si>
   <si>
     <t>1. 面板尺寸(英寸):46
@@ -413,7 +567,7 @@
 11. 重量(kg):11.3</t>
   </si>
   <si>
-    <t>55寸3.5拼缝液晶拼接屏（SK1）</t>
+    <t>55寸3.5mm拼缝液晶拼接屏（SK1）</t>
   </si>
   <si>
     <t>MW-D55-SK1</t>
@@ -432,10 +586,13 @@
 11. 重量(kg):18.2</t>
   </si>
   <si>
+    <t>46寸1.7mm拼缝液晶拼接屏</t>
+  </si>
+  <si>
+    <t>MW-D46-S3</t>
+  </si>
+  <si>
     <t>46寸1.7拼缝液晶拼接屏</t>
-  </si>
-  <si>
-    <t>MW-D46-S3</t>
   </si>
   <si>
     <t>1. 面板尺寸(英寸):46
@@ -451,10 +608,13 @@
 11. 重量(kg):20</t>
   </si>
   <si>
+    <t>55寸1.7mm拼缝液晶拼接屏</t>
+  </si>
+  <si>
+    <t>MW-D55-S3</t>
+  </si>
+  <si>
     <t>55寸1.7拼缝液晶拼接屏</t>
-  </si>
-  <si>
-    <t>MW-D55-S3</t>
   </si>
   <si>
     <t>1. 面板尺寸(英寸):55
@@ -470,10 +630,13 @@
 11. 重量(kg):20</t>
   </si>
   <si>
+    <t>65寸3.5mm拼缝液晶拼接屏</t>
+  </si>
+  <si>
+    <t>MW-D65-S1-4K</t>
+  </si>
+  <si>
     <t>65寸3.5拼缝液晶拼接屏</t>
-  </si>
-  <si>
-    <t>MW-D65-S1-4K</t>
   </si>
   <si>
     <t>1. 面板尺寸(英寸):65
@@ -488,6 +651,44 @@
 10. 功耗(W):270
 11. 重量(kg):30</t>
   </si>
+  <si>
+    <t>55寸0.88mm拼缝标亮LCD拼接显示单元</t>
+  </si>
+  <si>
+    <t>MW5255-S6-D</t>
+  </si>
+  <si>
+    <t>55寸0.88mm拼缝LCD拼接显示单元</t>
+  </si>
+  <si>
+    <t xml:space="preserve">面板尺寸（inches）:55
+拼缝（mm）:0.88
+点距（H*V）（mm）:0.63*0.63
+分辨率:1920*1080
+色彩数:16.7M
+亮度（cd/m²）:500
+对比度:4000：1
+刷新率:60Hz
+响应时间（ms）:8
+视角（H/V）:178°/178°
+视频输出:1*HDMI（为HDMI-A口环出）
+视频输入:2*HDMI，1*DVI，1*VGA
+（最高分辨率：1920*1080@60Hz）
+其它接口:1*USB 2.0，2*RS232(RJ45接头)，1*红外接口（3.5mm接口），1*按钮
+电源环接:支持
+输入电压:AC100-240V 50/60Hz 
+维护方式:后维护
+整机功耗（W）:230
+包装尺寸（W*H*D）（mm）:单包：1342*841*222
+双包：1342*841*352
+产品尺寸（W*H*D）（mm）:1211.7*682.6*122.5
+重量（Kg）:单包净重：24.5
+单包毛重：28.75
+双包净重：49
+双包毛重：54.64
+使用寿命（h）:50000
+</t>
+  </si>
 </sst>
 </file>
 
@@ -499,7 +700,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -528,6 +729,19 @@
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1017,28 +1231,19 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1047,125 +1252,134 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1194,9 +1408,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1208,6 +1434,9 @@
     </xf>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1735,7 +1964,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
@@ -1842,7 +2071,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="8">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:6">
@@ -2069,241 +2298,346 @@
       <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="5">
-        <v>4600</v>
+      <c r="F17" s="10">
+        <v>4800</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="5">
-        <v>6900</v>
+      <c r="F18" s="10">
+        <v>7200</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="5">
-        <v>9200</v>
+      <c r="F19" s="10">
+        <v>9600</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="9" t="s">
+      <c r="D20" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F20" s="5">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="E20" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="10">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="5">
-        <v>2990</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+        <v>76</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="10">
+        <v>144000</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>75</v>
+      <c r="B22" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F22" s="5">
-        <v>4320</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:6">
-      <c r="A23" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>79</v>
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="D23" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F23" s="13">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="24" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:6">
-      <c r="A24" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="11" t="s">
+      <c r="F23" s="5">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>83</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="F24" s="5">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="13">
+      <c r="B25" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="5">
         <v>1750</v>
-      </c>
-    </row>
-    <row r="25" s="3" customFormat="1" ht="26.1" customHeight="1" spans="2:6">
-      <c r="B25" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="14">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="26" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:6">
-      <c r="A26" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26" s="14">
-        <v>4100</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:6">
       <c r="A27" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" s="14">
-        <v>4250</v>
+        <v>96</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" s="17">
+        <v>1800</v>
       </c>
     </row>
     <row r="28" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:6">
       <c r="A28" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>98</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="F28" s="14">
+        <v>99</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="17">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="29" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:6">
+      <c r="A29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" s="18">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="30" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:6">
+      <c r="A30" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" s="18">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="31" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:6">
+      <c r="A31" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31" s="18">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="32" s="3" customFormat="1" ht="26.1" customHeight="1" spans="1:6">
+      <c r="A32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="18">
         <v>7600</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:6">
+      <c r="A33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F33">
+        <f>11700*0.58</f>
+        <v>6786</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>